--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/6.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/6.xlsx
@@ -426,13 +426,13 @@
         <v>-13.20135372989129</v>
       </c>
       <c r="E2">
-        <v>-4.249870778004056</v>
+        <v>-4.245749866657076</v>
       </c>
       <c r="F2">
-        <v>-2.269848600926365</v>
+        <v>-1.448741010044994</v>
       </c>
       <c r="G2">
-        <v>-4.925453701185616</v>
+        <v>-4.509864022131027</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.44949313334598</v>
       </c>
       <c r="E3">
-        <v>-4.311023291003637</v>
+        <v>-4.404617791794167</v>
       </c>
       <c r="F3">
-        <v>-2.342346487651974</v>
+        <v>-1.42525430907342</v>
       </c>
       <c r="G3">
-        <v>-5.367512994560246</v>
+        <v>-5.43987705483224</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.79081533830526</v>
       </c>
       <c r="E4">
-        <v>-5.670742896546738</v>
+        <v>-5.309203117196359</v>
       </c>
       <c r="F4">
-        <v>-2.426423293933916</v>
+        <v>-1.427113993892704</v>
       </c>
       <c r="G4">
-        <v>-4.880632214683602</v>
+        <v>-4.516331309824693</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.336665256586</v>
       </c>
       <c r="E5">
-        <v>-5.624389436604225</v>
+        <v>-6.474995351834986</v>
       </c>
       <c r="F5">
-        <v>-2.136430918664074</v>
+        <v>-1.066021187705775</v>
       </c>
       <c r="G5">
-        <v>-4.687683262102015</v>
+        <v>-4.487696089275419</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.04833575393864</v>
       </c>
       <c r="E6">
-        <v>-7.071707843351701</v>
+        <v>-7.131832392751541</v>
       </c>
       <c r="F6">
-        <v>-1.886188581584968</v>
+        <v>-1.314256390567897</v>
       </c>
       <c r="G6">
-        <v>-5.060023159781563</v>
+        <v>-4.796527943671915</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.92859896166028</v>
       </c>
       <c r="E7">
-        <v>-7.386599811949067</v>
+        <v>-7.364351419149383</v>
       </c>
       <c r="F7">
-        <v>-1.964089908879039</v>
+        <v>-1.376691270084299</v>
       </c>
       <c r="G7">
-        <v>-4.796954502474643</v>
+        <v>-3.893535770512729</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.95312367134575</v>
       </c>
       <c r="E8">
-        <v>-7.733231854866195</v>
+        <v>-7.815228933723082</v>
       </c>
       <c r="F8">
-        <v>-1.902369910431253</v>
+        <v>-0.9052342464549878</v>
       </c>
       <c r="G8">
-        <v>-4.862224561735117</v>
+        <v>-4.32884887236114</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.08842233038375</v>
       </c>
       <c r="E9">
-        <v>-8.810750545673303</v>
+        <v>-10.6121367496585</v>
       </c>
       <c r="F9">
-        <v>-1.770642926038076</v>
+        <v>-0.8751877040206443</v>
       </c>
       <c r="G9">
-        <v>-4.348759324783851</v>
+        <v>-4.100518507704061</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.30508401042645</v>
       </c>
       <c r="E10">
-        <v>-9.273026229324309</v>
+        <v>-9.50348480004866</v>
       </c>
       <c r="F10">
-        <v>-1.545082624092785</v>
+        <v>-0.9303478610056605</v>
       </c>
       <c r="G10">
-        <v>-4.760404975523988</v>
+        <v>-3.720831954952916</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.55219284839914</v>
       </c>
       <c r="E11">
-        <v>-9.446475840766098</v>
+        <v>-10.73921025878774</v>
       </c>
       <c r="F11">
-        <v>-1.530712106389019</v>
+        <v>-0.2585692334595538</v>
       </c>
       <c r="G11">
-        <v>-4.272536547957951</v>
+        <v>-3.084002631031207</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.80061713039282</v>
       </c>
       <c r="E12">
-        <v>-10.46709425566683</v>
+        <v>-11.2668182369474</v>
       </c>
       <c r="F12">
-        <v>-0.9121163228374461</v>
+        <v>-0.3474406302688988</v>
       </c>
       <c r="G12">
-        <v>-3.993143813392792</v>
+        <v>-3.588592163664175</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.00463593790057</v>
       </c>
       <c r="E13">
-        <v>-10.54617952573678</v>
+        <v>-12.25531618571173</v>
       </c>
       <c r="F13">
-        <v>-0.9043445798643812</v>
+        <v>0.121664658303864</v>
       </c>
       <c r="G13">
-        <v>-3.843270737443595</v>
+        <v>-3.265870898406549</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.14401714432539</v>
       </c>
       <c r="E14">
-        <v>-11.64082037676689</v>
+        <v>-12.18922310756978</v>
       </c>
       <c r="F14">
-        <v>-0.9222472561736841</v>
+        <v>0.3414520678190456</v>
       </c>
       <c r="G14">
-        <v>-3.192191068289218</v>
+        <v>-2.674115715046933</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.19938132505297</v>
       </c>
       <c r="E15">
-        <v>-12.4112224888478</v>
+        <v>-12.60719673000375</v>
       </c>
       <c r="F15">
-        <v>-0.8255370186316474</v>
+        <v>0.2137782851277663</v>
       </c>
       <c r="G15">
-        <v>-2.594355781379951</v>
+        <v>-2.750614114483827</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.16008231415363</v>
       </c>
       <c r="E16">
-        <v>-13.09796557211101</v>
+        <v>-13.38046536613151</v>
       </c>
       <c r="F16">
-        <v>-0.1878838146112692</v>
+        <v>0.4081613231338926</v>
       </c>
       <c r="G16">
-        <v>-2.003112468583607</v>
+        <v>-2.346344649809322</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.04115007039814</v>
       </c>
       <c r="E17">
-        <v>-13.77688798076298</v>
+        <v>-15.01357347599168</v>
       </c>
       <c r="F17">
-        <v>-0.09098967950581105</v>
+        <v>0.6972151581363634</v>
       </c>
       <c r="G17">
-        <v>-1.510535488079766</v>
+        <v>-1.060177985381301</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.85044490525219</v>
       </c>
       <c r="E18">
-        <v>-15.36102064423019</v>
+        <v>-14.55086305883594</v>
       </c>
       <c r="F18">
-        <v>0.0483226651948014</v>
+        <v>0.7167488898617784</v>
       </c>
       <c r="G18">
-        <v>-1.430024154675672</v>
+        <v>-1.009581548934663</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.62575261971999</v>
       </c>
       <c r="E19">
-        <v>-15.59153355664263</v>
+        <v>-16.73329317972255</v>
       </c>
       <c r="F19">
-        <v>0.2069939560988383</v>
+        <v>1.100455297777732</v>
       </c>
       <c r="G19">
-        <v>-0.6701687096041425</v>
+        <v>-0.7895493936014196</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.38745530821769</v>
       </c>
       <c r="E20">
-        <v>-16.70788844053952</v>
+        <v>-16.89170372898487</v>
       </c>
       <c r="F20">
-        <v>0.5206627284754963</v>
+        <v>1.484001002417542</v>
       </c>
       <c r="G20">
-        <v>-0.4856393715440906</v>
+        <v>0.2278688190002817</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.17453130854666</v>
       </c>
       <c r="E21">
-        <v>-17.11765193959758</v>
+        <v>-19.21722457156585</v>
       </c>
       <c r="F21">
-        <v>1.054331800789855</v>
+        <v>1.856731542246402</v>
       </c>
       <c r="G21">
-        <v>-0.09129560208690578</v>
+        <v>-0.5498200652468292</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.00757615953796</v>
       </c>
       <c r="E22">
-        <v>-18.47340007343596</v>
+        <v>-18.45533599061936</v>
       </c>
       <c r="F22">
-        <v>1.14294557533693</v>
+        <v>1.770417315609499</v>
       </c>
       <c r="G22">
-        <v>-0.08086131752787158</v>
+        <v>0.2551160828299107</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.90293718456485</v>
       </c>
       <c r="E23">
-        <v>-19.46064816337417</v>
+        <v>-18.99805095806861</v>
       </c>
       <c r="F23">
-        <v>1.324258632461685</v>
+        <v>2.232349770841421</v>
       </c>
       <c r="G23">
-        <v>0.1875786994718601</v>
+        <v>0.8148957620927386</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.87122315833438</v>
       </c>
       <c r="E24">
-        <v>-19.11046126836102</v>
+        <v>-20.3471331781677</v>
       </c>
       <c r="F24">
-        <v>1.382446472303934</v>
+        <v>2.040514790966306</v>
       </c>
       <c r="G24">
-        <v>-0.2737479268998292</v>
+        <v>-0.1841147975604779</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.89751366598598</v>
       </c>
       <c r="E25">
-        <v>-19.53962022159393</v>
+        <v>-19.37117457393061</v>
       </c>
       <c r="F25">
-        <v>1.523199347918015</v>
+        <v>2.474481562679717</v>
       </c>
       <c r="G25">
-        <v>0.3296260620017812</v>
+        <v>0.521938457600836</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.97565334226388</v>
       </c>
       <c r="E26">
-        <v>-19.40115307186139</v>
+        <v>-19.75907007200563</v>
       </c>
       <c r="F26">
-        <v>1.591306059041385</v>
+        <v>3.014075118658898</v>
       </c>
       <c r="G26">
-        <v>-0.3503578878697444</v>
+        <v>-0.2488336115989655</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.06977450337825</v>
       </c>
       <c r="E27">
-        <v>-19.6409131281975</v>
+        <v>-19.91584131367717</v>
       </c>
       <c r="F27">
-        <v>1.684543780430886</v>
+        <v>2.323960578651824</v>
       </c>
       <c r="G27">
-        <v>-1.000905999131491</v>
+        <v>-0.25696119740171</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.1627311391556</v>
       </c>
       <c r="E28">
-        <v>-19.18317950397619</v>
+        <v>-19.92915049878572</v>
       </c>
       <c r="F28">
-        <v>1.682209441089797</v>
+        <v>2.869148928069513</v>
       </c>
       <c r="G28">
-        <v>-0.3559983077304299</v>
+        <v>0.02518776327338164</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.22014091978745</v>
       </c>
       <c r="E29">
-        <v>-19.56713070119052</v>
+        <v>-19.99878031512766</v>
       </c>
       <c r="F29">
-        <v>1.693553104303733</v>
+        <v>2.561589365288501</v>
       </c>
       <c r="G29">
-        <v>-1.139675421323527</v>
+        <v>-0.960189320800342</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.2266381970563</v>
       </c>
       <c r="E30">
-        <v>-19.38128212791574</v>
+        <v>-20.65670871828006</v>
       </c>
       <c r="F30">
-        <v>1.679454291108085</v>
+        <v>2.322789267144266</v>
       </c>
       <c r="G30">
-        <v>-1.384736734712215</v>
+        <v>-1.027017960301553</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.16958778449266</v>
       </c>
       <c r="E31">
-        <v>-19.05943895171659</v>
+        <v>-19.91896596074247</v>
       </c>
       <c r="F31">
-        <v>1.428639552153646</v>
+        <v>1.770526660106669</v>
       </c>
       <c r="G31">
-        <v>-1.482215264800199</v>
+        <v>0.2962166640835152</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.03762993415781</v>
       </c>
       <c r="E32">
-        <v>-19.19131717176797</v>
+        <v>-19.57294073334237</v>
       </c>
       <c r="F32">
-        <v>1.303247921657079</v>
+        <v>2.041825268197535</v>
       </c>
       <c r="G32">
-        <v>-2.03405766911073</v>
+        <v>-0.4822236199007087</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.84151554672119</v>
       </c>
       <c r="E33">
-        <v>-18.42648508271649</v>
+        <v>-19.4910749802317</v>
       </c>
       <c r="F33">
-        <v>1.276905838248054</v>
+        <v>2.326823416395899</v>
       </c>
       <c r="G33">
-        <v>-1.530616564023568</v>
+        <v>-0.6143879430935824</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.58194551477523</v>
       </c>
       <c r="E34">
-        <v>-17.89763630267873</v>
+        <v>-19.18688379571446</v>
       </c>
       <c r="F34">
-        <v>1.271541330947525</v>
+        <v>2.406421240130904</v>
       </c>
       <c r="G34">
-        <v>-2.163249205570747</v>
+        <v>-1.27899608873755</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.28510411341258</v>
       </c>
       <c r="E35">
-        <v>-18.21728769745815</v>
+        <v>-18.89002421061564</v>
       </c>
       <c r="F35">
-        <v>1.255159537189762</v>
+        <v>1.823591875930005</v>
       </c>
       <c r="G35">
-        <v>-1.468716319304644</v>
+        <v>-1.35132077435083</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.961968488980641</v>
       </c>
       <c r="E36">
-        <v>-17.96943072959633</v>
+        <v>-19.29029602815362</v>
       </c>
       <c r="F36">
-        <v>1.1176671156731</v>
+        <v>1.736169293708157</v>
       </c>
       <c r="G36">
-        <v>-2.096686345015851</v>
+        <v>-1.358693679194903</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.642330443852554</v>
       </c>
       <c r="E37">
-        <v>-17.32979736143492</v>
+        <v>-18.25810283368929</v>
       </c>
       <c r="F37">
-        <v>0.9298695985192297</v>
+        <v>1.820603126340705</v>
       </c>
       <c r="G37">
-        <v>-2.005064795411477</v>
+        <v>-1.006300327375219</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.344365204171774</v>
       </c>
       <c r="E38">
-        <v>-17.02120902865623</v>
+        <v>-18.48708512188714</v>
       </c>
       <c r="F38">
-        <v>0.9754911048610097</v>
+        <v>2.208655149651744</v>
       </c>
       <c r="G38">
-        <v>-1.835783293938164</v>
+        <v>-0.600728217741614</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.082959602184474</v>
       </c>
       <c r="E39">
-        <v>-16.17258658504083</v>
+        <v>-17.04072675162929</v>
       </c>
       <c r="F39">
-        <v>1.109254216330268</v>
+        <v>1.667565562143107</v>
       </c>
       <c r="G39">
-        <v>-0.8330780788090132</v>
+        <v>0.1940984867104767</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.876427872776224</v>
       </c>
       <c r="E40">
-        <v>-16.36220284869</v>
+        <v>-18.36572201848157</v>
       </c>
       <c r="F40">
-        <v>0.9383520807238966</v>
+        <v>2.21883578503215</v>
       </c>
       <c r="G40">
-        <v>-0.9066660347226798</v>
+        <v>-0.3614779477347025</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.723194064315814</v>
       </c>
       <c r="E41">
-        <v>-16.10388510587046</v>
+        <v>-16.37363271708536</v>
       </c>
       <c r="F41">
-        <v>0.8621323392575085</v>
+        <v>1.97681499442583</v>
       </c>
       <c r="G41">
-        <v>-0.7564746802822169</v>
+        <v>0.7618449719196364</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.634142388882985</v>
       </c>
       <c r="E42">
-        <v>-15.70715908348048</v>
+        <v>-16.28668148766408</v>
       </c>
       <c r="F42">
-        <v>0.6722125448176659</v>
+        <v>1.783039978093358</v>
       </c>
       <c r="G42">
-        <v>-0.4698206024060076</v>
+        <v>-0.3056742126732263</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.595110898761353</v>
       </c>
       <c r="E43">
-        <v>-15.5915154427466</v>
+        <v>-15.90645722455806</v>
       </c>
       <c r="F43">
-        <v>0.7929553774497218</v>
+        <v>1.511910356952663</v>
       </c>
       <c r="G43">
-        <v>0.02350777783494594</v>
+        <v>-0.5209814089608696</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.606453563199691</v>
       </c>
       <c r="E44">
-        <v>-15.07492977032161</v>
+        <v>-16.38188359672733</v>
       </c>
       <c r="F44">
-        <v>0.624843183255979</v>
+        <v>1.496880458796269</v>
       </c>
       <c r="G44">
-        <v>0.7488480533226759</v>
+        <v>0.2951404234120173</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.651133491826606</v>
       </c>
       <c r="E45">
-        <v>-14.42465901671618</v>
+        <v>-15.73611414628553</v>
       </c>
       <c r="F45">
-        <v>0.6312961653237871</v>
+        <v>1.72759237761957</v>
       </c>
       <c r="G45">
-        <v>0.04473071888143436</v>
+        <v>0.6255594344481001</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.718328969642867</v>
       </c>
       <c r="E46">
-        <v>-14.26575939226103</v>
+        <v>-14.39230759840538</v>
       </c>
       <c r="F46">
-        <v>0.4542732229781299</v>
+        <v>1.690880791062302</v>
       </c>
       <c r="G46">
-        <v>0.3994996751101565</v>
+        <v>0.8691343544703597</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.797908948157648</v>
       </c>
       <c r="E47">
-        <v>-13.65593696849211</v>
+        <v>-14.92229755389308</v>
       </c>
       <c r="F47">
-        <v>0.2144948229311878</v>
+        <v>1.211648710990315</v>
       </c>
       <c r="G47">
-        <v>0.5038556455867362</v>
+        <v>0.07665372343327199</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.871731517900017</v>
       </c>
       <c r="E48">
-        <v>-13.4477041481974</v>
+        <v>-13.39819887034555</v>
       </c>
       <c r="F48">
-        <v>0.08124364251685937</v>
+        <v>1.37361276232048</v>
       </c>
       <c r="G48">
-        <v>0.8289820462474348</v>
+        <v>1.535993418104107</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.938271903052888</v>
       </c>
       <c r="E49">
-        <v>-13.67401010825672</v>
+        <v>-13.79126135726332</v>
       </c>
       <c r="F49">
-        <v>0.09702072807057874</v>
+        <v>1.277913133009859</v>
       </c>
       <c r="G49">
-        <v>0.8982026962654804</v>
+        <v>0.7294002531398471</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.98104865263346</v>
       </c>
       <c r="E50">
-        <v>-13.13129514080747</v>
+        <v>-13.23748785628734</v>
       </c>
       <c r="F50">
-        <v>-0.00432588182492677</v>
+        <v>1.6164619203296</v>
       </c>
       <c r="G50">
-        <v>1.278798147388592</v>
+        <v>0.4607896126190243</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.003132875189966</v>
       </c>
       <c r="E51">
-        <v>-12.39133343100612</v>
+        <v>-12.51408224745803</v>
       </c>
       <c r="F51">
-        <v>0.04195251986727321</v>
+        <v>1.417998344497283</v>
       </c>
       <c r="G51">
-        <v>0.9275400982284757</v>
+        <v>1.160293549547686</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.994578657761929</v>
       </c>
       <c r="E52">
-        <v>-11.78784181389992</v>
+        <v>-13.72676230197207</v>
       </c>
       <c r="F52">
-        <v>0.1157186370865692</v>
+        <v>0.9784284956713367</v>
       </c>
       <c r="G52">
-        <v>0.8214778925409847</v>
+        <v>0.7582815653060795</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.960509460378399</v>
       </c>
       <c r="E53">
-        <v>-11.43129241290599</v>
+        <v>-11.53919236308675</v>
       </c>
       <c r="F53">
-        <v>-0.06545442594711348</v>
+        <v>1.195159229470188</v>
       </c>
       <c r="G53">
-        <v>0.5762164246371705</v>
+        <v>0.2599821344025672</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.903386706190425</v>
       </c>
       <c r="E54">
-        <v>-11.02704459518928</v>
+        <v>-11.12324296853422</v>
       </c>
       <c r="F54">
-        <v>-0.2116852951959074</v>
+        <v>1.051215482620524</v>
       </c>
       <c r="G54">
-        <v>0.3717306970525758</v>
+        <v>0.2176871885013248</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.823561274957672</v>
       </c>
       <c r="E55">
-        <v>-11.68119625101928</v>
+        <v>-12.01893889945935</v>
       </c>
       <c r="F55">
-        <v>-0.1983104751103066</v>
+        <v>1.172965610014384</v>
       </c>
       <c r="G55">
-        <v>0.3920742707211331</v>
+        <v>0.6130940737437697</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.732433090208005</v>
       </c>
       <c r="E56">
-        <v>-10.86174623696129</v>
+        <v>-11.54230342473002</v>
       </c>
       <c r="F56">
-        <v>-0.09852119593206415</v>
+        <v>0.8134541571993984</v>
       </c>
       <c r="G56">
-        <v>0.2048838619763715</v>
+        <v>0.06408664486059874</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.62607429571996</v>
       </c>
       <c r="E57">
-        <v>-10.88160359548493</v>
+        <v>-10.54148802666484</v>
       </c>
       <c r="F57">
-        <v>-0.3022730692638529</v>
+        <v>0.8168388664072371</v>
       </c>
       <c r="G57">
-        <v>-0.1224639256800711</v>
+        <v>-0.1949132977126105</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.514852315717318</v>
       </c>
       <c r="E58">
-        <v>-9.82771901052385</v>
+        <v>-10.34213554389917</v>
       </c>
       <c r="F58">
-        <v>-0.2589726483847172</v>
+        <v>0.4899244992598151</v>
       </c>
       <c r="G58">
-        <v>-0.05735464627600963</v>
+        <v>-0.3625541884062004</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.392309326780932</v>
       </c>
       <c r="E59">
-        <v>-9.294359870374443</v>
+        <v>-11.04621362566374</v>
       </c>
       <c r="F59">
-        <v>-0.2693421515329614</v>
+        <v>0.9070977786162713</v>
       </c>
       <c r="G59">
-        <v>-0.1338661705991415</v>
+        <v>0.397599847827238</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.26779246098353</v>
       </c>
       <c r="E60">
-        <v>-10.64158088765637</v>
+        <v>-10.14799080624233</v>
       </c>
       <c r="F60">
-        <v>-0.2969027633915037</v>
+        <v>1.063037942193278</v>
       </c>
       <c r="G60">
-        <v>-0.8570375586360786</v>
+        <v>0.2579871516944248</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.141936937084678</v>
       </c>
       <c r="E61">
-        <v>-9.66284180037858</v>
+        <v>-10.18859763266911</v>
       </c>
       <c r="F61">
-        <v>-0.09576853105256139</v>
+        <v>1.320691682425231</v>
       </c>
       <c r="G61">
-        <v>-1.039283166490757</v>
+        <v>-1.154237482604343</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.018831850896692</v>
       </c>
       <c r="E62">
-        <v>-9.662547449568082</v>
+        <v>-10.02643297845443</v>
       </c>
       <c r="F62">
-        <v>-0.3637130795294923</v>
+        <v>0.8266185719646881</v>
       </c>
       <c r="G62">
-        <v>-0.9893560992422461</v>
+        <v>-1.159126502727916</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.906696867571674</v>
       </c>
       <c r="E63">
-        <v>-9.07399073973918</v>
+        <v>-9.201358599678917</v>
       </c>
       <c r="F63">
-        <v>-0.5623199629224933</v>
+        <v>0.7423719503651728</v>
       </c>
       <c r="G63">
-        <v>-1.633840513062139</v>
+        <v>-1.47955091289393</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.802185513374908</v>
       </c>
       <c r="E64">
-        <v>-8.940849075439663</v>
+        <v>-10.00278981566039</v>
       </c>
       <c r="F64">
-        <v>-0.5192224920570435</v>
+        <v>0.4594646014914744</v>
       </c>
       <c r="G64">
-        <v>-1.200082710232905</v>
+        <v>-1.782007353800425</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.715282649946849</v>
       </c>
       <c r="E65">
-        <v>-9.495953947773904</v>
+        <v>-9.151309904946144</v>
       </c>
       <c r="F65">
-        <v>-0.4370542442711521</v>
+        <v>0.4659672856034506</v>
       </c>
       <c r="G65">
-        <v>-1.272876610529186</v>
+        <v>-2.59595701750096</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.638841363760517</v>
       </c>
       <c r="E66">
-        <v>-8.979943391547883</v>
+        <v>-10.27153663411959</v>
       </c>
       <c r="F66">
-        <v>-0.8411376619285705</v>
+        <v>0.3251854171302718</v>
       </c>
       <c r="G66">
-        <v>-1.658052646949282</v>
+        <v>-2.113837290107069</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.580280789658206</v>
       </c>
       <c r="E67">
-        <v>-8.595548403880791</v>
+        <v>-9.9333683091228</v>
       </c>
       <c r="F67">
-        <v>-0.8169443635624082</v>
+        <v>0.518164372388653</v>
       </c>
       <c r="G67">
-        <v>-1.845492428532561</v>
+        <v>-2.635151209028527</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.533512088908373</v>
       </c>
       <c r="E68">
-        <v>-8.712346805486625</v>
+        <v>-9.130392883504715</v>
       </c>
       <c r="F68">
-        <v>-0.8366951275473568</v>
+        <v>0.1380166308351263</v>
       </c>
       <c r="G68">
-        <v>-1.709836885600438</v>
+        <v>-1.624899184312653</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.50008711509535</v>
       </c>
       <c r="E69">
-        <v>-9.301080125801827</v>
+        <v>-9.342923225632699</v>
       </c>
       <c r="F69">
-        <v>-1.03964348449843</v>
+        <v>0.1158445489317947</v>
       </c>
       <c r="G69">
-        <v>-2.126972020009526</v>
+        <v>-1.644468389693181</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.478928577556688</v>
       </c>
       <c r="E70">
-        <v>-8.951504574779712</v>
+        <v>-8.712926450159607</v>
       </c>
       <c r="F70">
-        <v>-1.060221787518775</v>
+        <v>-0.3530685584035186</v>
       </c>
       <c r="G70">
-        <v>-1.482848540561172</v>
+        <v>-2.237844496503163</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.461403163447973</v>
       </c>
       <c r="E71">
-        <v>-8.874665427817561</v>
+        <v>-10.24667078334347</v>
       </c>
       <c r="F71">
-        <v>-0.6884289595898845</v>
+        <v>0.1075310536772989</v>
       </c>
       <c r="G71">
-        <v>-2.475477124281269</v>
+        <v>-1.858371223153382</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.452398071677039</v>
       </c>
       <c r="E72">
-        <v>-8.806557178742199</v>
+        <v>-9.624136933035022</v>
       </c>
       <c r="F72">
-        <v>-0.9863720051917967</v>
+        <v>-0.1575026117461946</v>
       </c>
       <c r="G72">
-        <v>-1.774453981770583</v>
+        <v>-1.964072494469334</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.445216679528767</v>
       </c>
       <c r="E73">
-        <v>-9.339259690160494</v>
+        <v>-9.402898335390287</v>
       </c>
       <c r="F73">
-        <v>-1.129574363215956</v>
+        <v>0.1554421675204167</v>
       </c>
       <c r="G73">
-        <v>-1.498552466944674</v>
+        <v>-2.968444570150683</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.449860935226876</v>
       </c>
       <c r="E74">
-        <v>-9.699943587923423</v>
+        <v>-9.886552944831504</v>
       </c>
       <c r="F74">
-        <v>-1.165214042354002</v>
+        <v>-0.02846367957510157</v>
       </c>
       <c r="G74">
-        <v>-1.94459844451403</v>
+        <v>-1.952027130124612</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.459939105136231</v>
       </c>
       <c r="E75">
-        <v>-10.0231679486949</v>
+        <v>-10.28981808368856</v>
       </c>
       <c r="F75">
-        <v>-1.41155725406813</v>
+        <v>-0.1268347937597513</v>
       </c>
       <c r="G75">
-        <v>-1.682917743926754</v>
+        <v>-1.700468998048224</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.480325110400279</v>
       </c>
       <c r="E76">
-        <v>-10.16041241044537</v>
+        <v>-11.63851538349699</v>
       </c>
       <c r="F76">
-        <v>-1.70704087685113</v>
+        <v>-0.5324448925405292</v>
       </c>
       <c r="G76">
-        <v>-1.487429125858157</v>
+        <v>-1.340066184401935</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.509367632172968</v>
       </c>
       <c r="E77">
-        <v>-10.87068997312644</v>
+        <v>-11.42340833965864</v>
       </c>
       <c r="F77">
-        <v>-1.537990970757418</v>
+        <v>-0.2529760967558516</v>
       </c>
       <c r="G77">
-        <v>-1.667463190381769</v>
+        <v>-1.4291480685193</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.542770788554193</v>
       </c>
       <c r="E78">
-        <v>-10.81059259457065</v>
+        <v>-11.89285259766379</v>
       </c>
       <c r="F78">
-        <v>-1.469857751877159</v>
+        <v>-0.4665714599351069</v>
       </c>
       <c r="G78">
-        <v>-1.014355726303655</v>
+        <v>-1.648291012809934</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.585328861839867</v>
       </c>
       <c r="E79">
-        <v>-11.80315711299386</v>
+        <v>-12.58338601367142</v>
       </c>
       <c r="F79">
-        <v>-1.505046799148082</v>
+        <v>-0.80381888206505</v>
       </c>
       <c r="G79">
-        <v>-1.190531074273361</v>
+        <v>-1.988947435111484</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.629060533364957</v>
       </c>
       <c r="E80">
-        <v>-12.32609170597761</v>
+        <v>-12.4587442950843</v>
       </c>
       <c r="F80">
-        <v>-1.56488557522411</v>
+        <v>-0.3687338143578601</v>
       </c>
       <c r="G80">
-        <v>-0.3321077335561129</v>
+        <v>-1.843156198782237</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.683068669940936</v>
       </c>
       <c r="E81">
-        <v>-12.40262291670724</v>
+        <v>-12.66860283754776</v>
       </c>
       <c r="F81">
-        <v>-1.83674167457706</v>
+        <v>-0.7033138934507888</v>
       </c>
       <c r="G81">
-        <v>-0.4418383449470631</v>
+        <v>-0.8955426936361622</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.741961486147308</v>
       </c>
       <c r="E82">
-        <v>-14.573922048483</v>
+        <v>-13.99920888369555</v>
       </c>
       <c r="F82">
-        <v>-1.808866283105454</v>
+        <v>-0.7257775606799058</v>
       </c>
       <c r="G82">
-        <v>-0.9012060820477639</v>
+        <v>-1.081020304726894</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.815568412007837</v>
       </c>
       <c r="E83">
-        <v>-14.20160902946837</v>
+        <v>-15.14620795120234</v>
       </c>
       <c r="F83">
-        <v>-1.896387441048236</v>
+        <v>-1.068491379300923</v>
       </c>
       <c r="G83">
-        <v>-0.6607844159441306</v>
+        <v>-0.9632802315093389</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.905373086576573</v>
       </c>
       <c r="E84">
-        <v>-15.81139549818904</v>
+        <v>-15.18471356568956</v>
       </c>
       <c r="F84">
-        <v>-1.872888314565619</v>
+        <v>-0.6355161633686632</v>
       </c>
       <c r="G84">
-        <v>-0.3363766028049505</v>
+        <v>-0.6591798986015621</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.01634163460889</v>
       </c>
       <c r="E85">
-        <v>-16.70001795271419</v>
+        <v>-16.45875444300754</v>
       </c>
       <c r="F85">
-        <v>-1.841104685687605</v>
+        <v>-0.5884483275415954</v>
       </c>
       <c r="G85">
-        <v>-0.6490212366535213</v>
+        <v>-1.345260358130536</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.160411800648292</v>
       </c>
       <c r="E86">
-        <v>-17.40693538768157</v>
+        <v>-18.25102030034129</v>
       </c>
       <c r="F86">
-        <v>-1.940379548708709</v>
+        <v>-1.065600377065153</v>
       </c>
       <c r="G86">
-        <v>-0.57250643110883</v>
+        <v>-0.8861255877605559</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.336094554568902</v>
       </c>
       <c r="E87">
-        <v>-18.89525006962049</v>
+        <v>-19.8251722070956</v>
       </c>
       <c r="F87">
-        <v>-1.826925520853886</v>
+        <v>-0.6494799526776546</v>
       </c>
       <c r="G87">
-        <v>-0.1611068719856515</v>
+        <v>0.2254144652738171</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.561060145005461</v>
       </c>
       <c r="E88">
-        <v>-20.79539776323897</v>
+        <v>-19.63383965179752</v>
       </c>
       <c r="F88">
-        <v>-1.814831356773013</v>
+        <v>-0.6932376323631356</v>
       </c>
       <c r="G88">
-        <v>0.07650606846309699</v>
+        <v>-0.03022878764408017</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.831784666915091</v>
       </c>
       <c r="E89">
-        <v>-22.305621202427</v>
+        <v>-22.13266972312605</v>
       </c>
       <c r="F89">
-        <v>-1.970857670559911</v>
+        <v>-0.4199468006685367</v>
       </c>
       <c r="G89">
-        <v>-0.2134817305175081</v>
+        <v>0.2858512851772293</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.162171769158149</v>
       </c>
       <c r="E90">
-        <v>-22.98294053128025</v>
+        <v>-24.16234535878593</v>
       </c>
       <c r="F90">
-        <v>-2.05100718698518</v>
+        <v>-0.7292674725479001</v>
       </c>
       <c r="G90">
-        <v>-0.1909003637454096</v>
+        <v>-0.5021570408743353</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.548250080833292</v>
       </c>
       <c r="E91">
-        <v>-24.7269147417962</v>
+        <v>-24.94049116141996</v>
       </c>
       <c r="F91">
-        <v>-1.904688510791689</v>
+        <v>-0.8210025354687229</v>
       </c>
       <c r="G91">
-        <v>-0.4724652669829201</v>
+        <v>-0.4604691209615902</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.99161328858944</v>
       </c>
       <c r="E92">
-        <v>-27.87699824558983</v>
+        <v>-27.92197504943401</v>
       </c>
       <c r="F92">
-        <v>-1.980163549962961</v>
+        <v>-0.1415623378141237</v>
       </c>
       <c r="G92">
-        <v>0.1042783277422371</v>
+        <v>-0.6848423324179793</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.49242164634522</v>
       </c>
       <c r="E93">
-        <v>-28.8273256869435</v>
+        <v>-29.43287549548619</v>
       </c>
       <c r="F93">
-        <v>-2.102631043527645</v>
+        <v>-0.6679732549451535</v>
       </c>
       <c r="G93">
-        <v>-0.2345832663662971</v>
+        <v>-0.1859982187355992</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.03457871646375</v>
       </c>
       <c r="E94">
-        <v>-31.86393242481592</v>
+        <v>-31.65458107144132</v>
       </c>
       <c r="F94">
-        <v>-1.934233890947339</v>
+        <v>-0.4592039602546081</v>
       </c>
       <c r="G94">
-        <v>-0.2077199054591232</v>
+        <v>-0.765012418779892</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.62137196477452</v>
       </c>
       <c r="E95">
-        <v>-33.86405071062774</v>
+        <v>-34.443376126192</v>
       </c>
       <c r="F95">
-        <v>-1.718326554346871</v>
+        <v>-0.7460601365374517</v>
       </c>
       <c r="G95">
-        <v>-0.8032583372767796</v>
+        <v>-0.9045168346012435</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.23397438584652</v>
       </c>
       <c r="E96">
-        <v>-35.98641741651362</v>
+        <v>-36.49298157595964</v>
       </c>
       <c r="F96">
-        <v>-1.623762616745487</v>
+        <v>-0.7694341795422454</v>
       </c>
       <c r="G96">
-        <v>-1.01279386484136</v>
+        <v>0.0359206389943253</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.86673786725227</v>
       </c>
       <c r="E97">
-        <v>-38.74181271122072</v>
+        <v>-38.23307035577701</v>
       </c>
       <c r="F97">
-        <v>-1.689788468953025</v>
+        <v>-0.628200022467138</v>
       </c>
       <c r="G97">
-        <v>-0.9492530093427128</v>
+        <v>-1.059931893764342</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.51042745905159</v>
       </c>
       <c r="E98">
-        <v>-41.23174206688718</v>
+        <v>-40.32114972071381</v>
       </c>
       <c r="F98">
-        <v>-1.632047119140885</v>
+        <v>-0.7090387405715362</v>
       </c>
       <c r="G98">
-        <v>-1.537835251454347</v>
+        <v>-1.300835899437214</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-14.14350701269989</v>
       </c>
       <c r="E99">
-        <v>-43.29098637358014</v>
+        <v>-42.49362851996857</v>
       </c>
       <c r="F99">
-        <v>-1.655137032126519</v>
+        <v>-0.7112388843933717</v>
       </c>
       <c r="G99">
-        <v>-1.546540332251553</v>
+        <v>-1.412426963452369</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.78385454581198</v>
       </c>
       <c r="E100">
-        <v>-45.91749224108094</v>
+        <v>-46.12684359445554</v>
       </c>
       <c r="F100">
-        <v>-1.840850376894946</v>
+        <v>-0.391957922862747</v>
       </c>
       <c r="G100">
-        <v>-2.077300888042652</v>
+        <v>-1.575700548250339</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-15.37035694959609</v>
       </c>
       <c r="E101">
-        <v>-47.90110650337179</v>
+        <v>-47.71942412618406</v>
       </c>
       <c r="F101">
-        <v>-1.514216826297073</v>
+        <v>-0.8970416928413008</v>
       </c>
       <c r="G101">
-        <v>-2.844945953096303</v>
+        <v>-2.854671493798497</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-15.97936473327306</v>
       </c>
       <c r="E102">
-        <v>-50.29202417121604</v>
+        <v>-50.19544653817296</v>
       </c>
       <c r="F102">
-        <v>-1.206802227811551</v>
+        <v>-0.7466954943353989</v>
       </c>
       <c r="G102">
-        <v>-2.984824428175431</v>
+        <v>-2.251432034980824</v>
       </c>
     </row>
   </sheetData>
